--- a/DataAnalysis/LT/0.3/Results.xlsx
+++ b/DataAnalysis/LT/0.3/Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LT\0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D7BD1A-14EC-4EF1-B02C-04574B825AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E67458-F286-46EC-B91F-EE8758E3F895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -461,15 +461,105 @@
       <c r="B2" t="s">
         <v>16</v>
       </c>
+      <c r="E2">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="G2">
+        <v>16.8</v>
+      </c>
+      <c r="H2">
+        <v>2.6373387259803289</v>
+      </c>
+      <c r="I2">
+        <v>12.85</v>
+      </c>
+      <c r="J2">
+        <v>1.8265024257063336</v>
+      </c>
+      <c r="K2">
+        <v>15.55</v>
+      </c>
+      <c r="L2">
+        <v>0.97831424676946177</v>
+      </c>
+      <c r="M2">
+        <v>2.9000000000000008</v>
+      </c>
+      <c r="N2">
+        <v>1.399294354793879</v>
+      </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>20</v>
       </c>
+      <c r="E3">
+        <v>20.3</v>
+      </c>
+      <c r="F3">
+        <v>1.6431676725154984</v>
+      </c>
+      <c r="G3">
+        <v>17.8</v>
+      </c>
+      <c r="H3">
+        <v>3.0331501776206182</v>
+      </c>
+      <c r="I3">
+        <v>11.4</v>
+      </c>
+      <c r="J3">
+        <v>1.7102631376487103</v>
+      </c>
+      <c r="K3">
+        <v>16.5</v>
+      </c>
+      <c r="L3">
+        <v>1.509230856356236</v>
+      </c>
+      <c r="M3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="N3">
+        <v>1.1155467020454322</v>
+      </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>21</v>
+      </c>
+      <c r="E4">
+        <v>21.5</v>
+      </c>
+      <c r="F4">
+        <v>3.7249161064378349</v>
+      </c>
+      <c r="G4">
+        <v>19.2</v>
+      </c>
+      <c r="H4">
+        <v>3.7013511046643481</v>
+      </c>
+      <c r="I4">
+        <v>14.1</v>
+      </c>
+      <c r="J4">
+        <v>2.3021728866442701</v>
+      </c>
+      <c r="K4">
+        <v>18.266666666666669</v>
+      </c>
+      <c r="L4">
+        <v>2.5620087605019757</v>
+      </c>
+      <c r="M4">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="N4">
+        <v>2.7105759945484329</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66F790C-5674-4FFE-AFAC-55716215CEA8}">
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -538,173 +628,353 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
+      <c r="B3">
+        <v>71</v>
+      </c>
+      <c r="C3">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>84</v>
+      </c>
+      <c r="G3">
+        <v>86</v>
+      </c>
+      <c r="H3">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>23</v>
+      </c>
+      <c r="J3">
+        <v>77</v>
+      </c>
+      <c r="L3">
+        <v>84</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+      <c r="N3">
+        <v>11</v>
+      </c>
+      <c r="O3">
+        <v>89</v>
+      </c>
+      <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
+        <v>22.5</v>
+      </c>
+      <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>18.5</v>
+      </c>
+      <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>18.166666666666668</v>
+      </c>
+      <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="V3">
         <f>T3-U3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X3" t="e">
+        <v>4.6666666666666679</v>
+      </c>
+      <c r="X3">
         <f>AVERAGE(Q3:Q7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y3" t="e">
+        <v>21.5</v>
+      </c>
+      <c r="Y3">
         <f>_xlfn.STDEV.S(Q3:Q7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z3" t="e">
+        <v>3.7249161064378349</v>
+      </c>
+      <c r="Z3">
         <f>AVERAGE(R3:R7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>19.2</v>
+      </c>
+      <c r="AA3">
         <f>_xlfn.STDEV.S(R3:R7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB3" t="e">
+        <v>3.7013511046643481</v>
+      </c>
+      <c r="AB3">
         <f>AVERAGE(S3:S7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC3" t="e">
+        <v>14.1</v>
+      </c>
+      <c r="AC3">
         <f>_xlfn.STDEV.S(S3:S7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD3" t="e">
+        <v>2.3021728866442701</v>
+      </c>
+      <c r="AD3">
         <f>AVERAGE(T3:T7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE3" t="e">
+        <v>18.266666666666669</v>
+      </c>
+      <c r="AE3">
         <f>_xlfn.STDEV.S(T3:T7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF3" t="e">
+        <v>2.5620087605019757</v>
+      </c>
+      <c r="AF3">
         <f>AVERAGE(V3:V7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG3" t="e">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AG3">
         <f>_xlfn.STDEV.S(V3:V7)</f>
-        <v>#DIV/0!</v>
+        <v>2.7105759945484329</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
+      <c r="B4">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>82</v>
+      </c>
+      <c r="G4">
+        <v>89</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>73</v>
+      </c>
+      <c r="L4">
+        <v>91</v>
+      </c>
+      <c r="M4">
+        <v>9</v>
+      </c>
+      <c r="N4">
+        <v>12</v>
+      </c>
+      <c r="O4">
+        <v>88</v>
+      </c>
+      <c r="Q4">
         <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
+        <v>19.5</v>
+      </c>
+      <c r="R4">
         <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
+        <v>19</v>
+      </c>
+      <c r="S4">
         <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+        <v>10.5</v>
+      </c>
+      <c r="T4">
         <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
+        <v>16.333333333333332</v>
+      </c>
+      <c r="U4">
         <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
+        <v>10.5</v>
+      </c>
+      <c r="V4">
         <f t="shared" ref="V4:V14" si="5">T4-U4</f>
-        <v>#DIV/0!</v>
+        <v>5.8333333333333321</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>86</v>
+      </c>
+      <c r="G5">
+        <v>85</v>
+      </c>
+      <c r="H5">
+        <v>15</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>82</v>
+      </c>
+      <c r="L5">
+        <v>85</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>18</v>
+      </c>
+      <c r="O5">
+        <v>82</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
+        <v>17</v>
+      </c>
+      <c r="R5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="S5">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="T5">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
+        <v>16.666666666666668</v>
+      </c>
+      <c r="U5">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.16666666666666785</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q6" t="e">
+      <c r="B6">
+        <v>75</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>82</v>
+      </c>
+      <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>83</v>
+      </c>
+      <c r="L6">
+        <v>83</v>
+      </c>
+      <c r="M6">
+        <v>17</v>
+      </c>
+      <c r="N6">
+        <v>12</v>
+      </c>
+      <c r="O6">
+        <v>88</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" t="e">
+        <v>21.5</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
+        <v>17.5</v>
+      </c>
+      <c r="U6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q7" t="e">
+      <c r="B7">
+        <v>71</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>75</v>
+      </c>
+      <c r="G7">
+        <v>81</v>
+      </c>
+      <c r="H7">
+        <v>19</v>
+      </c>
+      <c r="I7">
+        <v>32</v>
+      </c>
+      <c r="J7">
+        <v>68</v>
+      </c>
+      <c r="L7">
+        <v>85</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <v>16</v>
+      </c>
+      <c r="O7">
+        <v>84</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R7" t="e">
+        <v>27</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" t="e">
+        <v>25.5</v>
+      </c>
+      <c r="S7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" t="e">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="U7">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.1666666666666679</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -738,43 +1008,43 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X9" t="e">
-        <f>AVERAGE(Q9:Q10)</f>
+        <f>AVERAGE(Q9:Q11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y9" t="e">
-        <f>_xlfn.STDEV.S(Q9:Q10)</f>
+        <f>_xlfn.STDEV.S(Q9:Q11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z9" t="e">
-        <f>AVERAGE(R9:R10)</f>
+        <f>AVERAGE(R9:R11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA9" t="e">
-        <f>_xlfn.STDEV.S(R9:R10)</f>
+        <f>_xlfn.STDEV.S(R9:R11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AB9" t="e">
-        <f>AVERAGE(S9:S10)</f>
+        <f>AVERAGE(S9:S11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AC9" t="e">
-        <f>_xlfn.STDEV.S(S9:S10)</f>
+        <f>_xlfn.STDEV.S(S9:S11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD9" t="e">
-        <f>AVERAGE(T9:T10)</f>
+        <f>AVERAGE(T9:T11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE9" t="e">
-        <f>_xlfn.STDEV.S(T9:T10)</f>
+        <f>_xlfn.STDEV.S(T9:T11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AF9" t="e">
-        <f>AVERAGE(V9:V10)</f>
+        <f>AVERAGE(V9:V11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AG9" t="e">
-        <f>_xlfn.STDEV.S(V9:V10)</f>
+        <f>_xlfn.STDEV.S(V9:V11)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -804,6 +1074,32 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q11" t="e">
+        <f t="shared" ref="Q11" si="6">AVERAGE(C11:D11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R11" t="e">
+        <f t="shared" ref="R11" si="7">AVERAGE(H11:I11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S11" t="e">
+        <f t="shared" ref="S11" si="8">AVERAGE(M11:N11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T11" t="e">
+        <f t="shared" ref="T11" si="9">AVERAGE(Q11:S11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" t="e">
+        <f t="shared" ref="U11" si="10">MIN(Q11:S11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V11" t="e">
+        <f t="shared" ref="V11" si="11">T11-U11</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
@@ -835,43 +1131,43 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X13" t="e">
-        <f>AVERAGE(Q13:Q14)</f>
+        <f>AVERAGE(Q13:Q15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y13" t="e">
-        <f>_xlfn.STDEV.S(Q13:Q14)</f>
+        <f>_xlfn.STDEV.S(Q13:Q15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z13" t="e">
-        <f>AVERAGE(R13:R14)</f>
+        <f>AVERAGE(R13:R15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA13" t="e">
-        <f>_xlfn.STDEV.S(R13:R14)</f>
+        <f>_xlfn.STDEV.S(R13:R15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AB13" t="e">
-        <f>AVERAGE(S13:S14)</f>
+        <f>AVERAGE(S13:S15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AC13" t="e">
-        <f>_xlfn.STDEV.S(S13:S14)</f>
+        <f>_xlfn.STDEV.S(S13:S15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD13" t="e">
-        <f>AVERAGE(T13:T14)</f>
+        <f>AVERAGE(T13:T15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE13" t="e">
-        <f>_xlfn.STDEV.S(T13:T14)</f>
+        <f>_xlfn.STDEV.S(T13:T15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AF13" t="e">
-        <f>AVERAGE(V13:V14)</f>
+        <f>AVERAGE(V13:V15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AG13" t="e">
-        <f>_xlfn.STDEV.S(V13:V14)</f>
+        <f>_xlfn.STDEV.S(V13:V15)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -898,6 +1194,32 @@
       </c>
       <c r="V14" t="e">
         <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q15" t="e">
+        <f t="shared" ref="Q15" si="12">AVERAGE(C15:D15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" t="e">
+        <f t="shared" ref="R15" si="13">AVERAGE(H15:I15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" t="e">
+        <f t="shared" ref="S15" si="14">AVERAGE(M15:N15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" t="e">
+        <f t="shared" ref="T15" si="15">AVERAGE(Q15:S15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" t="e">
+        <f t="shared" ref="U15" si="16">MIN(Q15:S15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" t="e">
+        <f t="shared" ref="V15" si="17">T15-U15</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -908,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FDE21E-9CB3-45CD-ADE0-EE4270AB04E7}">
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -967,173 +1289,353 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
+      <c r="B3">
+        <v>82</v>
+      </c>
+      <c r="C3">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>22</v>
+      </c>
+      <c r="J3">
+        <v>78</v>
+      </c>
+      <c r="L3">
+        <v>90</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>12</v>
+      </c>
+      <c r="O3">
+        <v>88</v>
+      </c>
+      <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
+        <v>19</v>
+      </c>
+      <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>16</v>
+      </c>
+      <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>11</v>
+      </c>
+      <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
+        <v>11</v>
+      </c>
+      <c r="V3">
         <f>T3-U3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X3" t="e">
+        <v>4.3333333333333339</v>
+      </c>
+      <c r="X3">
         <f>AVERAGE(Q3:Q7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y3" t="e">
+        <v>20.3</v>
+      </c>
+      <c r="Y3">
         <f>_xlfn.STDEV.S(Q3:Q7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z3" t="e">
+        <v>1.6431676725154984</v>
+      </c>
+      <c r="Z3">
         <f>AVERAGE(R3:R7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>17.8</v>
+      </c>
+      <c r="AA3">
         <f>_xlfn.STDEV.S(R3:R7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB3" t="e">
+        <v>3.0331501776206182</v>
+      </c>
+      <c r="AB3">
         <f>AVERAGE(S3:S7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC3" t="e">
+        <v>11.4</v>
+      </c>
+      <c r="AC3">
         <f>_xlfn.STDEV.S(S3:S7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD3" t="e">
+        <v>1.7102631376487103</v>
+      </c>
+      <c r="AD3">
         <f>AVERAGE(T3:T7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE3" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="AE3">
         <f>_xlfn.STDEV.S(T3:T7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF3" t="e">
+        <v>1.509230856356236</v>
+      </c>
+      <c r="AF3">
         <f>AVERAGE(V3:V7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG3" t="e">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AG3">
         <f>_xlfn.STDEV.S(V3:V7)</f>
-        <v>#DIV/0!</v>
+        <v>1.1155467020454322</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
+      <c r="B4">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>82</v>
+      </c>
+      <c r="L4">
+        <v>90</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>91</v>
+      </c>
+      <c r="Q4">
         <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
+        <v>20.5</v>
+      </c>
+      <c r="R4">
         <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
+        <v>14</v>
+      </c>
+      <c r="S4">
         <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+        <v>9.5</v>
+      </c>
+      <c r="T4">
         <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="U4">
         <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
+        <v>9.5</v>
+      </c>
+      <c r="V4">
         <f t="shared" ref="V4:V14" si="5">T4-U4</f>
-        <v>#DIV/0!</v>
+        <v>5.1666666666666661</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
+      <c r="B5">
+        <v>75</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>87</v>
+      </c>
+      <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>28</v>
+      </c>
+      <c r="J5">
+        <v>72</v>
+      </c>
+      <c r="L5">
+        <v>85</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>13</v>
+      </c>
+      <c r="O5">
+        <v>87</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
+        <v>19</v>
+      </c>
+      <c r="R5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
+        <v>22</v>
+      </c>
+      <c r="S5">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
+        <v>14</v>
+      </c>
+      <c r="T5">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
+        <v>18.333333333333332</v>
+      </c>
+      <c r="U5">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" t="e">
+        <v>14</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>4.3333333333333321</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q6" t="e">
+      <c r="B6">
+        <v>72</v>
+      </c>
+      <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>88</v>
+      </c>
+      <c r="G6">
+        <v>87</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>77</v>
+      </c>
+      <c r="L6">
+        <v>79</v>
+      </c>
+      <c r="M6">
+        <v>21</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>97</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" t="e">
+        <v>20</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
+        <v>18</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
+        <v>12</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
+        <v>16.666666666666668</v>
+      </c>
+      <c r="U6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" t="e">
+        <v>12</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>4.6666666666666679</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q7" t="e">
+      <c r="B7">
+        <v>73</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>81</v>
+      </c>
+      <c r="G7">
+        <v>86</v>
+      </c>
+      <c r="H7">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>76</v>
+      </c>
+      <c r="L7">
+        <v>90</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>11</v>
+      </c>
+      <c r="O7">
+        <v>89</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R7" t="e">
+        <v>23</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" t="e">
+        <v>19</v>
+      </c>
+      <c r="S7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" t="e">
+        <v>10.5</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" t="e">
+        <v>17.5</v>
+      </c>
+      <c r="U7">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" t="e">
+        <v>10.5</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -1167,43 +1669,43 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X9" t="e">
-        <f>AVERAGE(Q9:Q10)</f>
+        <f>AVERAGE(Q9:Q11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y9" t="e">
-        <f>_xlfn.STDEV.S(Q9:Q10)</f>
+        <f>_xlfn.STDEV.S(Q9:Q11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z9" t="e">
-        <f>AVERAGE(R9:R10)</f>
+        <f>AVERAGE(R9:R11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA9" t="e">
-        <f>_xlfn.STDEV.S(R9:R10)</f>
+        <f>_xlfn.STDEV.S(R9:R11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AB9" t="e">
-        <f>AVERAGE(S9:S10)</f>
+        <f>AVERAGE(S9:S11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AC9" t="e">
-        <f>_xlfn.STDEV.S(S9:S10)</f>
+        <f>_xlfn.STDEV.S(S9:S11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD9" t="e">
-        <f>AVERAGE(T9:T10)</f>
+        <f>AVERAGE(T9:T11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE9" t="e">
-        <f>_xlfn.STDEV.S(T9:T10)</f>
+        <f>_xlfn.STDEV.S(T9:T11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AF9" t="e">
-        <f>AVERAGE(V9:V10)</f>
+        <f>AVERAGE(V9:V11)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AG9" t="e">
-        <f>_xlfn.STDEV.S(V9:V10)</f>
+        <f>_xlfn.STDEV.S(V9:V11)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1233,6 +1735,32 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q11" t="e">
+        <f t="shared" ref="Q11" si="6">AVERAGE(C11:D11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R11" t="e">
+        <f t="shared" ref="R11" si="7">AVERAGE(H11:I11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S11" t="e">
+        <f t="shared" ref="S11" si="8">AVERAGE(M11:N11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T11" t="e">
+        <f t="shared" ref="T11" si="9">AVERAGE(Q11:S11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" t="e">
+        <f t="shared" ref="U11" si="10">MIN(Q11:S11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V11" t="e">
+        <f t="shared" ref="V11" si="11">T11-U11</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
@@ -1264,43 +1792,43 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X13" t="e">
-        <f>AVERAGE(Q13:Q14)</f>
+        <f>AVERAGE(Q13:Q15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y13" t="e">
-        <f>_xlfn.STDEV.S(Q13:Q14)</f>
+        <f>_xlfn.STDEV.S(Q13:Q15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z13" t="e">
-        <f>AVERAGE(R13:R14)</f>
+        <f>AVERAGE(R13:R15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA13" t="e">
-        <f>_xlfn.STDEV.S(R13:R14)</f>
+        <f>_xlfn.STDEV.S(R13:R15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AB13" t="e">
-        <f>AVERAGE(S13:S14)</f>
+        <f>AVERAGE(S13:S15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AC13" t="e">
-        <f>_xlfn.STDEV.S(S13:S14)</f>
+        <f>_xlfn.STDEV.S(S13:S15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD13" t="e">
-        <f>AVERAGE(T13:T14)</f>
+        <f>AVERAGE(T13:T15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE13" t="e">
-        <f>_xlfn.STDEV.S(T13:T14)</f>
+        <f>_xlfn.STDEV.S(T13:T15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AF13" t="e">
-        <f>AVERAGE(V13:V14)</f>
+        <f>AVERAGE(V13:V15)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AG13" t="e">
-        <f>_xlfn.STDEV.S(V13:V14)</f>
+        <f>_xlfn.STDEV.S(V13:V15)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1327,6 +1855,32 @@
       </c>
       <c r="V14" t="e">
         <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q15" t="e">
+        <f t="shared" ref="Q15" si="12">AVERAGE(C15:D15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" t="e">
+        <f t="shared" ref="R15" si="13">AVERAGE(H15:I15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" t="e">
+        <f t="shared" ref="S15" si="14">AVERAGE(M15:N15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" t="e">
+        <f t="shared" ref="T15" si="15">AVERAGE(Q15:S15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" t="e">
+        <f t="shared" ref="U15" si="16">MIN(Q15:S15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" t="e">
+        <f t="shared" ref="V15" si="17">T15-U15</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1337,10 +1891,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F52E050-0D53-43C0-B5FC-AD6D7416AA3A}">
-  <dimension ref="Q1:AG11"/>
+  <dimension ref="B1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="17:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:33" x14ac:dyDescent="0.3">
       <c r="Q1" t="s">
         <v>0</v>
       </c>
@@ -1390,304 +1944,664 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q2" t="e">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>80</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>90</v>
+      </c>
+      <c r="G2">
+        <v>82</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+      <c r="I2">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>81</v>
+      </c>
+      <c r="L2">
+        <v>83</v>
+      </c>
+      <c r="M2">
+        <v>17</v>
+      </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+      <c r="O2">
+        <v>90</v>
+      </c>
+      <c r="Q2">
         <f>AVERAGE(C2:D2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R2" t="e">
+        <v>15</v>
+      </c>
+      <c r="R2">
         <f>AVERAGE(H2:I2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S2" t="e">
+        <v>18.5</v>
+      </c>
+      <c r="S2">
         <f>AVERAGE(M2:N2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T2" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="T2">
         <f>AVERAGE(Q2:S2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U2" t="e">
+        <v>15.666666666666666</v>
+      </c>
+      <c r="U2">
         <f>MIN(Q2:S2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V2" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="V2">
         <f>T2-U2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" t="e">
-        <f>AVERAGE(Q2:Q11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" t="e">
-        <f>_xlfn.STDEV.S(Q2:Q11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2" t="e">
-        <f>AVERAGE(R2:R11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2" t="e">
-        <f>_xlfn.STDEV.S(R2:R11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2" t="e">
-        <f>AVERAGE(S2:S11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2" t="e">
-        <f>_xlfn.STDEV.S(S2:S11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2" t="e">
-        <f>AVERAGE(T2:T11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE2" t="e">
-        <f>_xlfn.STDEV.S(T2:T11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF2" t="e">
-        <f>AVERAGE(V2:V11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2" t="e">
-        <f>_xlfn.STDEV.S(V2:V11)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="3" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
+        <v>2.1666666666666661</v>
+      </c>
+      <c r="X2">
+        <f>AVERAGE(Q2:Q21)</f>
+        <v>17</v>
+      </c>
+      <c r="Y2">
+        <f>_xlfn.STDEV.S(Q2:Q21)</f>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="Z2">
+        <f>AVERAGE(R2:R21)</f>
+        <v>16.8</v>
+      </c>
+      <c r="AA2">
+        <f>_xlfn.STDEV.S(R2:R21)</f>
+        <v>2.6373387259803289</v>
+      </c>
+      <c r="AB2">
+        <f>AVERAGE(S2:S21)</f>
+        <v>12.85</v>
+      </c>
+      <c r="AC2">
+        <f>_xlfn.STDEV.S(S2:S21)</f>
+        <v>1.8265024257063336</v>
+      </c>
+      <c r="AD2">
+        <f>AVERAGE(T2:T21)</f>
+        <v>15.55</v>
+      </c>
+      <c r="AE2">
+        <f>_xlfn.STDEV.S(T2:T21)</f>
+        <v>0.97831424676946177</v>
+      </c>
+      <c r="AF2">
+        <f>AVERAGE(V2:V21)</f>
+        <v>2.9000000000000008</v>
+      </c>
+      <c r="AG2">
+        <f>_xlfn.STDEV.S(V2:V21)</f>
+        <v>1.399294354793879</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>87</v>
+      </c>
+      <c r="G3">
+        <v>89</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>82</v>
+      </c>
+      <c r="L3">
+        <v>85</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>11</v>
+      </c>
+      <c r="O3">
+        <v>89</v>
+      </c>
+      <c r="Q3">
         <f t="shared" ref="Q3:Q11" si="0">AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
+        <v>17</v>
+      </c>
+      <c r="R3">
         <f t="shared" ref="R3:R11" si="1">AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="S3">
         <f t="shared" ref="S3:S11" si="2">AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>13</v>
+      </c>
+      <c r="T3">
         <f t="shared" ref="T3:T11" si="3">AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>14.833333333333334</v>
+      </c>
+      <c r="U3">
         <f t="shared" ref="U3:U11" si="4">MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
+        <v>13</v>
+      </c>
+      <c r="V3">
         <f t="shared" ref="V3:V11" si="5">T3-U3</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
+        <v>1.8333333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>83</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>89</v>
+      </c>
+      <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>24</v>
+      </c>
+      <c r="J4">
+        <v>76</v>
+      </c>
+      <c r="L4">
+        <v>87</v>
+      </c>
+      <c r="M4">
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
+        <v>90</v>
+      </c>
+      <c r="Q4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
+        <v>14</v>
+      </c>
+      <c r="R4">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
+        <v>20</v>
+      </c>
+      <c r="S4">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+        <v>11.5</v>
+      </c>
+      <c r="T4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
+        <v>15.166666666666666</v>
+      </c>
+      <c r="U4">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
+        <v>11.5</v>
+      </c>
+      <c r="V4">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
+        <v>3.6666666666666661</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>73</v>
+      </c>
+      <c r="C5">
+        <v>27</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>89</v>
+      </c>
+      <c r="G5">
+        <v>87</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>86</v>
+      </c>
+      <c r="L5">
+        <v>86</v>
+      </c>
+      <c r="M5">
+        <v>14</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>90</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
+        <v>19</v>
+      </c>
+      <c r="R5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="S5">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
+        <v>12</v>
+      </c>
+      <c r="T5">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
+        <v>14.833333333333334</v>
+      </c>
+      <c r="U5">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" t="e">
+        <v>12</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q6" t="e">
+        <v>2.8333333333333339</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>77</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>83</v>
+      </c>
+      <c r="G6">
+        <v>79</v>
+      </c>
+      <c r="H6">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>82</v>
+      </c>
+      <c r="L6">
+        <v>85</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <v>12</v>
+      </c>
+      <c r="O6">
+        <v>88</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" t="e">
+        <v>20</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
+        <v>19.5</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="U6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q7" t="e">
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>80</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>88</v>
+      </c>
+      <c r="G7">
+        <v>86</v>
+      </c>
+      <c r="H7">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>22</v>
+      </c>
+      <c r="J7">
+        <v>78</v>
+      </c>
+      <c r="L7">
+        <v>87</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>7</v>
+      </c>
+      <c r="O7">
+        <v>93</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R7" t="e">
+        <v>16</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" t="e">
+        <v>18</v>
+      </c>
+      <c r="S7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" t="e">
+        <v>10</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" t="e">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="U7">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" t="e">
+        <v>10</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q8" t="e">
+        <v>4.6666666666666661</v>
+      </c>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>88</v>
+      </c>
+      <c r="G8">
+        <v>81</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>89</v>
+      </c>
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>14</v>
+      </c>
+      <c r="O8">
+        <v>86</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R8" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" t="e">
+        <v>15</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" t="e">
+        <v>17</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
+        <v>15.833333333333334</v>
+      </c>
+      <c r="U8">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" t="e">
+        <v>15</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q9" t="e">
+        <v>0.83333333333333393</v>
+      </c>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>28</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>83</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>86</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>11</v>
+      </c>
+      <c r="O9">
+        <v>89</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
+        <v>21</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
+        <v>14</v>
+      </c>
+      <c r="S9">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
+        <v>12.5</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" t="e">
+        <v>15.833333333333334</v>
+      </c>
+      <c r="U9">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V9" t="e">
+        <v>12.5</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q10" t="e">
+        <v>3.3333333333333339</v>
+      </c>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>80</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="G10">
+        <v>86</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="L10">
+        <v>86</v>
+      </c>
+      <c r="M10">
+        <v>14</v>
+      </c>
+      <c r="N10">
+        <v>13</v>
+      </c>
+      <c r="O10">
+        <v>87</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
+        <v>15</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
+        <v>15</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q11" t="e">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>87</v>
+      </c>
+      <c r="G11">
+        <v>83</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>77</v>
+      </c>
+      <c r="L11">
+        <v>83</v>
+      </c>
+      <c r="M11">
+        <v>17</v>
+      </c>
+      <c r="N11">
+        <v>7</v>
+      </c>
+      <c r="O11">
+        <v>93</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R11" t="e">
+        <v>17.5</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S11" t="e">
+        <v>20</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T11" t="e">
+        <v>12</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U11" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="U11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V11" t="e">
+        <v>12</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/LT/0.3/Results.xlsx
+++ b/DataAnalysis/LT/0.3/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LT\0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E67458-F286-46EC-B91F-EE8758E3F895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036ABA8C-6141-4FD2-A80C-8906C035E924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,143 +422,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
+      <c r="B2">
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="D2">
+        <v>16.8</v>
+      </c>
       <c r="E2">
-        <v>17</v>
+        <v>2.6373387259803289</v>
       </c>
       <c r="F2">
-        <v>2.3452078799117149</v>
+        <v>12.85</v>
       </c>
       <c r="G2">
-        <v>16.8</v>
+        <v>1.8265024257063336</v>
       </c>
       <c r="H2">
-        <v>2.6373387259803289</v>
+        <v>15.55</v>
       </c>
       <c r="I2">
-        <v>12.85</v>
+        <v>0.97831424676946177</v>
       </c>
       <c r="J2">
-        <v>1.8265024257063336</v>
+        <v>2.9000000000000008</v>
       </c>
       <c r="K2">
-        <v>15.55</v>
-      </c>
-      <c r="L2">
-        <v>0.97831424676946177</v>
-      </c>
-      <c r="M2">
-        <v>2.9000000000000008</v>
-      </c>
-      <c r="N2">
         <v>1.399294354793879</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
+      <c r="B3">
+        <v>20.3</v>
+      </c>
+      <c r="C3">
+        <v>1.6431676725154984</v>
+      </c>
+      <c r="D3">
+        <v>17.8</v>
+      </c>
       <c r="E3">
-        <v>20.3</v>
+        <v>3.0331501776206182</v>
       </c>
       <c r="F3">
-        <v>1.6431676725154984</v>
+        <v>11.4</v>
       </c>
       <c r="G3">
-        <v>17.8</v>
+        <v>1.7102631376487103</v>
       </c>
       <c r="H3">
-        <v>3.0331501776206182</v>
+        <v>16.5</v>
       </c>
       <c r="I3">
-        <v>11.4</v>
+        <v>1.509230856356236</v>
       </c>
       <c r="J3">
-        <v>1.7102631376487103</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="K3">
-        <v>16.5</v>
-      </c>
-      <c r="L3">
-        <v>1.509230856356236</v>
-      </c>
-      <c r="M3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="N3">
         <v>1.1155467020454322</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>21</v>
       </c>
+      <c r="B4">
+        <v>21.5</v>
+      </c>
+      <c r="C4">
+        <v>3.7249161064378349</v>
+      </c>
+      <c r="D4">
+        <v>19.2</v>
+      </c>
       <c r="E4">
-        <v>21.5</v>
+        <v>3.7013511046643481</v>
       </c>
       <c r="F4">
-        <v>3.7249161064378349</v>
+        <v>14.1</v>
       </c>
       <c r="G4">
-        <v>19.2</v>
+        <v>2.3021728866442701</v>
       </c>
       <c r="H4">
-        <v>3.7013511046643481</v>
+        <v>18.266666666666669</v>
       </c>
       <c r="I4">
-        <v>14.1</v>
+        <v>2.5620087605019757</v>
       </c>
       <c r="J4">
-        <v>2.3021728866442701</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K4">
-        <v>18.266666666666669</v>
-      </c>
-      <c r="L4">
-        <v>2.5620087605019757</v>
-      </c>
-      <c r="M4">
-        <v>4.166666666666667</v>
-      </c>
-      <c r="N4">
         <v>2.7105759945484329</v>
       </c>
     </row>
